--- a/basedatos_partidas/salida/descompuestos/CT-06-01-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-01-060.xlsx
@@ -539,10 +539,10 @@
         <v>0.026</v>
       </c>
       <c r="G10" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H10" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>5.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>7.56</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="12">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>15.15</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>22.63</v>
+        <v>21.61</v>
       </c>
       <c r="H28" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="29">
@@ -925,7 +925,7 @@
       </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>22.86</v>
+        <v>21.83</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-01-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-01-060.xlsx
@@ -617,10 +617,10 @@
         <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="14">
@@ -643,10 +643,10 @@
         <v>0.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="15">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14.13</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="17">
@@ -906,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>21.61</v>
+        <v>21.63</v>
       </c>
       <c r="H28" t="n">
         <v>0.22</v>
@@ -925,7 +925,7 @@
       </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-01-060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-01-060.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 06 Paredes y tabiquería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Bloque de concreto</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
